--- a/Server-Doku-23-02-2026-01_44_01.xlsx
+++ b/Server-Doku-23-02-2026-01_44_01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lrcuasa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asi\Documents\GitHub\rvtools-analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95C7874-AD76-4FD7-8C66-830D5AC8B9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C319CF9D-8A49-49C3-B192-511ED7086623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6480" yWindow="2363" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Server Doku" sheetId="1" r:id="rId1"/>
@@ -223,9 +223,6 @@
     <t>WINTER Simon</t>
   </si>
   <si>
-    <t>MICHIAPP1101</t>
-  </si>
-  <si>
     <t>10.18.77.129</t>
   </si>
   <si>
@@ -236,6 +233,9 @@
   </si>
   <si>
     <t>2025-11-20T13:10:00</t>
+  </si>
+  <si>
+    <t>servername1101</t>
   </si>
 </sst>
 </file>
@@ -613,12 +613,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AO2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="26.796875" customWidth="1"/>
+    <col min="1" max="1" width="26.8125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -743,9 +743,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:41" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
         <v>41</v>
@@ -766,7 +766,7 @@
         <v>46</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
         <v>56</v>
@@ -778,7 +778,7 @@
         <v>59</v>
       </c>
       <c r="M2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N2" t="s">
         <v>61</v>
@@ -817,13 +817,13 @@
         <v>51</v>
       </c>
       <c r="Z2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AA2" t="s">
         <v>57</v>
       </c>
       <c r="AB2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AC2" t="s">
         <v>52</v>
@@ -860,7 +860,7 @@
   <autoFilter ref="A1:AO2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AO1 A2:AO2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AO1 B2:AO2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
